--- a/main/StructureDefinition-ConsentModule.xlsx
+++ b/main/StructureDefinition-ConsentModule.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4963" uniqueCount="740">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4963" uniqueCount="741">
   <si>
     <t>Property</t>
   </si>
@@ -561,7 +561,7 @@
     <t>A human language.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/languages|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/languages</t>
   </si>
   <si>
     <t>Resource.language</t>
@@ -754,7 +754,7 @@
     <t>A coded type for an identifier that can be used to determine which identifier to use for a specific purpose.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/identifier-type|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/identifier-type</t>
   </si>
   <si>
     <t>Identifier.type</t>
@@ -839,7 +839,7 @@
     <t>Questionnaire.identifier.assigner</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(Organization|4.0.1)
+    <t xml:space="preserve">Reference(Organization)
 </t>
   </si>
   <si>
@@ -922,7 +922,7 @@
     <t>Questionnaire.derivedFrom</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(Questionnaire|4.0.1)
+    <t xml:space="preserve">canonical(Questionnaire)
 </t>
   </si>
   <si>
@@ -1326,6 +1326,9 @@
   </si>
   <si>
     <t>Aa resource (or, for logical models, the URI of the logical model).</t>
+  </si>
+  <si>
+    <t>http://hl7.org/fhir/ValueSet/resource-types</t>
   </si>
   <si>
     <t>Reference.type</t>
@@ -1379,7 +1382,7 @@
     <t>Countries and regions within which this artifact is targeted for use.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/jurisdiction|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/jurisdiction</t>
   </si>
   <si>
     <t>Definition.jurisdiction</t>
@@ -1501,7 +1504,7 @@
     <t>Codes for questionnaires, groups and individual questions.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/questionnaire-questions|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/questionnaire-questions</t>
   </si>
   <si>
     <t>.code</t>
@@ -1564,6 +1567,10 @@
   <si>
     <t xml:space="preserve">ele-1
 </t>
+  </si>
+  <si>
+    <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
+ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
     <t>Questionnaire.item.extension:xacmlTemplate.id</t>
@@ -1864,10 +1871,6 @@
 In diesem Fall muss der reine Textinhalt identisch sein.</t>
   </si>
   <si>
-    <t xml:space="preserve">cm-1
-</t>
-  </si>
-  <si>
     <t>ele-1:All FHIR elements must have a @value or children {hasValue() or (children().count() &gt; id.count())}
 cm-1:Wenn der Text im Markdown-Format angegeben ist, muss er auch als Klartext angegeben sein. {extension('http://hl7.org/fhir/StructureDefinition/rendering-markdown').empty() or hasValue()}</t>
   </si>
@@ -2073,7 +2076,7 @@
   </si>
   <si>
     <t>boolean
-decimalintegerdatedateTimetimestringCodingQuantityReference(Resource|4.0.1)</t>
+decimalintegerdatedateTimetimestringCodingQuantityReference(Resource)</t>
   </si>
   <si>
     <t>Value for question comparison based on operator</t>
@@ -2085,7 +2088,7 @@
     <t>Allowed values to answer questions.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/questionnaire-answers|4.0.1</t>
+    <t>http://hl7.org/fhir/ValueSet/questionnaire-answers</t>
   </si>
   <si>
     <t xml:space="preserve">que-7
@@ -2192,7 +2195,7 @@
     <t>Questionnaire.item.answerValueSet</t>
   </si>
   <si>
-    <t xml:space="preserve">canonical(ValueSet|4.0.1)
+    <t xml:space="preserve">canonical(ValueSet)
 </t>
   </si>
   <si>
@@ -2234,7 +2237,7 @@
   </si>
   <si>
     <t>integer
-datetimestringCodingReference(Resource|4.0.1)</t>
+datetimestringCodingReference(Resource)</t>
   </si>
   <si>
     <t>Answer value</t>
@@ -2293,7 +2296,7 @@
   </si>
   <si>
     <t>boolean
-decimalintegerdatedateTimetimestringuriAttachmentCodingQuantityReference(Resource|4.0.1)</t>
+decimalintegerdatedateTimetimestringuriAttachmentCodingQuantityReference(Resource)</t>
   </si>
   <si>
     <t>Actual value for initializing the question</t>
@@ -9206,7 +9209,7 @@
         <v>423</v>
       </c>
       <c r="Z56" t="s" s="2">
-        <v>319</v>
+        <v>424</v>
       </c>
       <c r="AA56" t="s" s="2">
         <v>21</v>
@@ -9224,7 +9227,7 @@
         <v>21</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>80</v>
@@ -9256,10 +9259,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -9285,13 +9288,13 @@
         <v>210</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="N57" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="O57" s="2"/>
       <c r="P57" t="s" s="2">
@@ -9341,7 +9344,7 @@
         <v>21</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>80</v>
@@ -9373,10 +9376,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -9402,13 +9405,13 @@
         <v>102</v>
       </c>
       <c r="L58" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="M58" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="N58" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="O58" s="2"/>
       <c r="P58" t="s" s="2">
@@ -9458,7 +9461,7 @@
         <v>21</v>
       </c>
       <c r="AF58" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AG58" t="s" s="2">
         <v>80</v>
@@ -9490,10 +9493,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9519,13 +9522,13 @@
         <v>231</v>
       </c>
       <c r="L59" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="M59" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="N59" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="O59" s="2"/>
       <c r="P59" t="s" s="2">
@@ -9554,10 +9557,10 @@
         <v>151</v>
       </c>
       <c r="Y59" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="Z59" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AA59" t="s" s="2">
         <v>21</v>
@@ -9575,7 +9578,7 @@
         <v>21</v>
       </c>
       <c r="AF59" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="AG59" t="s" s="2">
         <v>80</v>
@@ -9590,7 +9593,7 @@
         <v>100</v>
       </c>
       <c r="AK59" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="AL59" t="s" s="2">
         <v>277</v>
@@ -9607,10 +9610,10 @@
     </row>
     <row r="60">
       <c r="A60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9636,13 +9639,13 @@
         <v>347</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="N60" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="O60" s="2"/>
       <c r="P60" t="s" s="2">
@@ -9692,7 +9695,7 @@
         <v>21</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>80</v>
@@ -9707,13 +9710,13 @@
         <v>100</v>
       </c>
       <c r="AK60" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="AL60" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="AM60" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="AN60" t="s" s="2">
         <v>217</v>
@@ -9724,14 +9727,14 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="E61" s="2"/>
       <c r="F61" t="s" s="2">
@@ -9753,14 +9756,14 @@
         <v>347</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N61" s="2"/>
       <c r="O61" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>21</v>
@@ -9809,7 +9812,7 @@
         <v>21</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>80</v>
@@ -9824,7 +9827,7 @@
         <v>100</v>
       </c>
       <c r="AK61" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AL61" t="s" s="2">
         <v>277</v>
@@ -9841,10 +9844,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9867,16 +9870,16 @@
         <v>21</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="N62" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="O62" s="2"/>
       <c r="P62" t="s" s="2">
@@ -9926,7 +9929,7 @@
         <v>21</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>80</v>
@@ -9941,10 +9944,10 @@
         <v>100</v>
       </c>
       <c r="AK62" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AL62" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="AM62" t="s" s="2">
         <v>21</v>
@@ -9958,10 +9961,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9984,19 +9987,19 @@
         <v>21</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>21</v>
@@ -10045,7 +10048,7 @@
         <v>21</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>80</v>
@@ -10060,10 +10063,10 @@
         <v>100</v>
       </c>
       <c r="AK63" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>21</v>
@@ -10077,10 +10080,10 @@
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -10106,16 +10109,16 @@
         <v>258</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="N64" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="O64" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="P64" t="s" s="2">
         <v>21</v>
@@ -10164,7 +10167,7 @@
         <v>21</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>80</v>
@@ -10179,7 +10182,7 @@
         <v>100</v>
       </c>
       <c r="AK64" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="AL64" t="s" s="2">
         <v>277</v>
@@ -10196,10 +10199,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -10225,14 +10228,14 @@
         <v>147</v>
       </c>
       <c r="L65" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="M65" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="N65" s="2"/>
       <c r="O65" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="P65" t="s" s="2">
         <v>21</v>
@@ -10260,10 +10263,10 @@
         <v>159</v>
       </c>
       <c r="Y65" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z65" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA65" t="s" s="2">
         <v>21</v>
@@ -10281,7 +10284,7 @@
         <v>21</v>
       </c>
       <c r="AF65" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="AG65" t="s" s="2">
         <v>80</v>
@@ -10299,7 +10302,7 @@
         <v>21</v>
       </c>
       <c r="AL65" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM65" t="s" s="2">
         <v>21</v>
@@ -10313,10 +10316,10 @@
     </row>
     <row r="66">
       <c r="A66" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -10339,16 +10342,16 @@
         <v>21</v>
       </c>
       <c r="K66" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
       <c r="O66" s="2"/>
       <c r="P66" t="s" s="2">
@@ -10398,7 +10401,7 @@
         <v>21</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>80</v>
@@ -10407,16 +10410,16 @@
         <v>81</v>
       </c>
       <c r="AI66" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AJ66" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="AK66" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL66" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="AM66" t="s" s="2">
         <v>21</v>
@@ -10430,10 +10433,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -10545,10 +10548,10 @@
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -10574,10 +10577,10 @@
         <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" s="2"/>
@@ -10658,13 +10661,13 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>494</v>
+        <v>495</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C69" t="s" s="2">
-        <v>495</v>
+        <v>496</v>
       </c>
       <c r="D69" t="s" s="2">
         <v>21</v>
@@ -10686,13 +10689,13 @@
         <v>21</v>
       </c>
       <c r="K69" t="s" s="2">
-        <v>496</v>
+        <v>497</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>497</v>
+        <v>498</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>498</v>
+        <v>499</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" s="2"/>
@@ -10752,10 +10755,10 @@
         <v>81</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AJ69" t="s" s="2">
-        <v>117</v>
+        <v>501</v>
       </c>
       <c r="AK69" t="s" s="2">
         <v>21</v>
@@ -10775,10 +10778,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>500</v>
+        <v>502</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>501</v>
+        <v>503</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10890,10 +10893,10 @@
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>502</v>
+        <v>504</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10919,10 +10922,10 @@
         <v>109</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N71" s="2"/>
       <c r="O71" s="2"/>
@@ -11005,13 +11008,13 @@
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C72" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="D72" t="s" s="2">
         <v>21</v>
@@ -11036,10 +11039,10 @@
         <v>109</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>506</v>
+        <v>508</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N72" s="2"/>
       <c r="O72" s="2"/>
@@ -11122,10 +11125,10 @@
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>507</v>
+        <v>509</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -11237,10 +11240,10 @@
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -11354,10 +11357,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -11383,13 +11386,13 @@
         <v>135</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N75" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O75" s="2"/>
       <c r="P75" t="s" s="2">
@@ -11397,7 +11400,7 @@
       </c>
       <c r="Q75" s="2"/>
       <c r="R75" t="s" s="2">
-        <v>505</v>
+        <v>507</v>
       </c>
       <c r="S75" t="s" s="2">
         <v>21</v>
@@ -11439,7 +11442,7 @@
         <v>21</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>88</v>
@@ -11471,10 +11474,10 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>517</v>
+        <v>519</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
@@ -11497,13 +11500,13 @@
         <v>21</v>
       </c>
       <c r="K76" t="s" s="2">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N76" s="2"/>
       <c r="O76" s="2"/>
@@ -11554,7 +11557,7 @@
         <v>21</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>80</v>
@@ -11586,13 +11589,13 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>503</v>
+        <v>505</v>
       </c>
       <c r="C77" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D77" t="s" s="2">
         <v>21</v>
@@ -11617,10 +11620,10 @@
         <v>109</v>
       </c>
       <c r="L77" t="s" s="2">
-        <v>525</v>
+        <v>527</v>
       </c>
       <c r="M77" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N77" s="2"/>
       <c r="O77" s="2"/>
@@ -11703,10 +11706,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>526</v>
+        <v>528</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11818,10 +11821,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>527</v>
+        <v>529</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11935,10 +11938,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>528</v>
+        <v>530</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11964,13 +11967,13 @@
         <v>135</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O80" s="2"/>
       <c r="P80" t="s" s="2">
@@ -11978,7 +11981,7 @@
       </c>
       <c r="Q80" s="2"/>
       <c r="R80" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="S80" t="s" s="2">
         <v>21</v>
@@ -12020,7 +12023,7 @@
         <v>21</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>88</v>
@@ -12052,10 +12055,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>529</v>
+        <v>531</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>518</v>
+        <v>520</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -12081,10 +12084,10 @@
         <v>102</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N81" s="2"/>
       <c r="O81" s="2"/>
@@ -12135,7 +12138,7 @@
         <v>21</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>80</v>
@@ -12167,10 +12170,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>530</v>
+        <v>532</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>531</v>
+        <v>533</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -12196,13 +12199,13 @@
         <v>135</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N82" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O82" s="2"/>
       <c r="P82" t="s" s="2">
@@ -12210,7 +12213,7 @@
       </c>
       <c r="Q82" s="2"/>
       <c r="R82" t="s" s="2">
-        <v>532</v>
+        <v>534</v>
       </c>
       <c r="S82" t="s" s="2">
         <v>21</v>
@@ -12252,7 +12255,7 @@
         <v>21</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>88</v>
@@ -12284,10 +12287,10 @@
     </row>
     <row r="83">
       <c r="A83" t="s" s="2">
-        <v>533</v>
+        <v>535</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>534</v>
+        <v>536</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -12310,13 +12313,13 @@
         <v>21</v>
       </c>
       <c r="K83" t="s" s="2">
-        <v>535</v>
+        <v>537</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" s="2"/>
@@ -12367,7 +12370,7 @@
         <v>21</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>80</v>
@@ -12399,13 +12402,13 @@
     </row>
     <row r="84">
       <c r="A84" t="s" s="2">
-        <v>536</v>
+        <v>538</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C84" t="s" s="2">
-        <v>537</v>
+        <v>539</v>
       </c>
       <c r="D84" t="s" s="2">
         <v>21</v>
@@ -12415,7 +12418,7 @@
         <v>80</v>
       </c>
       <c r="G84" t="s" s="2">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H84" t="s" s="2">
         <v>89</v>
@@ -12427,16 +12430,16 @@
         <v>21</v>
       </c>
       <c r="K84" t="s" s="2">
-        <v>538</v>
+        <v>540</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>539</v>
+        <v>541</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>540</v>
+        <v>542</v>
       </c>
       <c r="N84" t="s" s="2">
-        <v>541</v>
+        <v>543</v>
       </c>
       <c r="O84" s="2"/>
       <c r="P84" t="s" s="2">
@@ -12495,10 +12498,10 @@
         <v>81</v>
       </c>
       <c r="AI84" t="s" s="2">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AJ84" t="s" s="2">
-        <v>117</v>
+        <v>501</v>
       </c>
       <c r="AK84" t="s" s="2">
         <v>21</v>
@@ -12518,13 +12521,13 @@
     </row>
     <row r="85">
       <c r="A85" t="s" s="2">
-        <v>542</v>
+        <v>544</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C85" t="s" s="2">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="D85" t="s" s="2">
         <v>21</v>
@@ -12548,16 +12551,16 @@
         <v>21</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>543</v>
+        <v>545</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>544</v>
+        <v>546</v>
       </c>
       <c r="O85" s="2"/>
       <c r="P85" t="s" s="2">
@@ -12639,13 +12642,13 @@
     </row>
     <row r="86">
       <c r="A86" t="s" s="2">
-        <v>545</v>
+        <v>547</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C86" t="s" s="2">
-        <v>546</v>
+        <v>548</v>
       </c>
       <c r="D86" t="s" s="2">
         <v>21</v>
@@ -12667,13 +12670,13 @@
         <v>21</v>
       </c>
       <c r="K86" t="s" s="2">
-        <v>547</v>
+        <v>549</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>548</v>
+        <v>550</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>549</v>
+        <v>551</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" s="2"/>
@@ -12756,19 +12759,19 @@
     </row>
     <row r="87">
       <c r="A87" t="s" s="2">
-        <v>550</v>
+        <v>552</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C87" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="D87" t="s" s="2">
         <v>21</v>
       </c>
       <c r="E87" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="F87" t="s" s="2">
         <v>80</v>
@@ -12786,13 +12789,13 @@
         <v>21</v>
       </c>
       <c r="K87" t="s" s="2">
-        <v>552</v>
+        <v>554</v>
       </c>
       <c r="L87" t="s" s="2">
-        <v>551</v>
+        <v>553</v>
       </c>
       <c r="M87" t="s" s="2">
-        <v>553</v>
+        <v>555</v>
       </c>
       <c r="N87" s="2"/>
       <c r="O87" s="2"/>
@@ -12875,13 +12878,13 @@
     </row>
     <row r="88">
       <c r="A88" t="s" s="2">
-        <v>554</v>
+        <v>556</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="C88" t="s" s="2">
-        <v>555</v>
+        <v>557</v>
       </c>
       <c r="D88" t="s" s="2">
         <v>21</v>
@@ -12903,16 +12906,16 @@
         <v>21</v>
       </c>
       <c r="K88" t="s" s="2">
-        <v>556</v>
+        <v>558</v>
       </c>
       <c r="L88" t="s" s="2">
-        <v>557</v>
+        <v>559</v>
       </c>
       <c r="M88" t="s" s="2">
-        <v>558</v>
+        <v>560</v>
       </c>
       <c r="N88" t="s" s="2">
-        <v>559</v>
+        <v>561</v>
       </c>
       <c r="O88" s="2"/>
       <c r="P88" t="s" s="2">
@@ -12994,14 +12997,14 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>560</v>
+        <v>562</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E89" s="2"/>
       <c r="F89" t="s" s="2">
@@ -13023,10 +13026,10 @@
         <v>109</v>
       </c>
       <c r="L89" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M89" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N89" t="s" s="2">
         <v>112</v>
@@ -13081,7 +13084,7 @@
         <v>21</v>
       </c>
       <c r="AF89" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG89" t="s" s="2">
         <v>80</v>
@@ -13113,10 +13116,10 @@
     </row>
     <row r="90">
       <c r="A90" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -13142,16 +13145,16 @@
         <v>102</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>566</v>
+        <v>568</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>567</v>
+        <v>569</v>
       </c>
       <c r="N90" t="s" s="2">
-        <v>568</v>
+        <v>570</v>
       </c>
       <c r="O90" t="s" s="2">
-        <v>569</v>
+        <v>571</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>21</v>
@@ -13200,7 +13203,7 @@
         <v>21</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>565</v>
+        <v>567</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>88</v>
@@ -13218,7 +13221,7 @@
         <v>21</v>
       </c>
       <c r="AL90" t="s" s="2">
-        <v>570</v>
+        <v>572</v>
       </c>
       <c r="AM90" t="s" s="2">
         <v>21</v>
@@ -13232,10 +13235,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -13261,16 +13264,16 @@
         <v>135</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>572</v>
+        <v>574</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>573</v>
+        <v>575</v>
       </c>
       <c r="N91" t="s" s="2">
-        <v>574</v>
+        <v>576</v>
       </c>
       <c r="O91" t="s" s="2">
-        <v>575</v>
+        <v>577</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>21</v>
@@ -13319,7 +13322,7 @@
         <v>21</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>571</v>
+        <v>573</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>80</v>
@@ -13337,7 +13340,7 @@
         <v>21</v>
       </c>
       <c r="AL91" t="s" s="2">
-        <v>576</v>
+        <v>578</v>
       </c>
       <c r="AM91" t="s" s="2">
         <v>21</v>
@@ -13351,10 +13354,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -13380,16 +13383,16 @@
         <v>147</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>578</v>
+        <v>580</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>579</v>
+        <v>581</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>580</v>
+        <v>582</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>581</v>
+        <v>583</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>21</v>
@@ -13417,10 +13420,10 @@
         <v>159</v>
       </c>
       <c r="Y92" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="Z92" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="AA92" t="s" s="2">
         <v>21</v>
@@ -13438,7 +13441,7 @@
         <v>21</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>577</v>
+        <v>579</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>80</v>
@@ -13447,7 +13450,7 @@
         <v>81</v>
       </c>
       <c r="AI92" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AJ92" t="s" s="2">
         <v>100</v>
@@ -13456,7 +13459,7 @@
         <v>21</v>
       </c>
       <c r="AL92" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AM92" t="s" s="2">
         <v>21</v>
@@ -13470,14 +13473,14 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
-        <v>583</v>
+        <v>585</v>
       </c>
       <c r="E93" s="2"/>
       <c r="F93" t="s" s="2">
@@ -13499,16 +13502,16 @@
         <v>102</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>584</v>
+        <v>586</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>585</v>
+        <v>587</v>
       </c>
       <c r="N93" t="s" s="2">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="O93" t="s" s="2">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>21</v>
@@ -13557,7 +13560,7 @@
         <v>21</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>582</v>
+        <v>584</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>80</v>
@@ -13575,7 +13578,7 @@
         <v>21</v>
       </c>
       <c r="AL93" t="s" s="2">
-        <v>588</v>
+        <v>590</v>
       </c>
       <c r="AM93" t="s" s="2">
         <v>21</v>
@@ -13589,10 +13592,10 @@
     </row>
     <row r="94">
       <c r="A94" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13618,13 +13621,13 @@
         <v>102</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>590</v>
+        <v>592</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>591</v>
+        <v>593</v>
       </c>
       <c r="N94" t="s" s="2">
-        <v>592</v>
+        <v>594</v>
       </c>
       <c r="O94" s="2"/>
       <c r="P94" t="s" s="2">
@@ -13674,7 +13677,7 @@
         <v>21</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>589</v>
+        <v>591</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>80</v>
@@ -13683,10 +13686,10 @@
         <v>88</v>
       </c>
       <c r="AI94" t="s" s="2">
-        <v>593</v>
+        <v>21</v>
       </c>
       <c r="AJ94" t="s" s="2">
-        <v>594</v>
+        <v>595</v>
       </c>
       <c r="AK94" t="s" s="2">
         <v>21</v>
@@ -13706,10 +13709,10 @@
     </row>
     <row r="95" hidden="true">
       <c r="A95" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="B95" t="s" s="2">
-        <v>595</v>
+        <v>596</v>
       </c>
       <c r="C95" s="2"/>
       <c r="D95" t="s" s="2">
@@ -13735,10 +13738,10 @@
         <v>102</v>
       </c>
       <c r="L95" t="s" s="2">
-        <v>596</v>
+        <v>597</v>
       </c>
       <c r="M95" t="s" s="2">
-        <v>597</v>
+        <v>598</v>
       </c>
       <c r="N95" s="2"/>
       <c r="O95" s="2"/>
@@ -13821,10 +13824,10 @@
     </row>
     <row r="96" hidden="true">
       <c r="A96" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="B96" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C96" s="2"/>
       <c r="D96" t="s" s="2">
@@ -13850,10 +13853,10 @@
         <v>109</v>
       </c>
       <c r="L96" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M96" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N96" s="2"/>
       <c r="O96" s="2"/>
@@ -13934,13 +13937,13 @@
     </row>
     <row r="97" hidden="true">
       <c r="A97" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="B97" t="s" s="2">
         <v>599</v>
       </c>
-      <c r="B97" t="s" s="2">
-        <v>598</v>
-      </c>
       <c r="C97" t="s" s="2">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="D97" t="s" s="2">
         <v>21</v>
@@ -13950,7 +13953,7 @@
         <v>80</v>
       </c>
       <c r="G97" t="s" s="2">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H97" t="s" s="2">
         <v>21</v>
@@ -13962,13 +13965,13 @@
         <v>21</v>
       </c>
       <c r="K97" t="s" s="2">
-        <v>601</v>
+        <v>602</v>
       </c>
       <c r="L97" t="s" s="2">
-        <v>602</v>
+        <v>603</v>
       </c>
       <c r="M97" t="s" s="2">
-        <v>603</v>
+        <v>604</v>
       </c>
       <c r="N97" s="2"/>
       <c r="O97" s="2"/>
@@ -14028,16 +14031,16 @@
         <v>81</v>
       </c>
       <c r="AI97" t="s" s="2">
-        <v>593</v>
+        <v>500</v>
       </c>
       <c r="AJ97" t="s" s="2">
-        <v>117</v>
+        <v>501</v>
       </c>
       <c r="AK97" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL97" t="s" s="2">
-        <v>604</v>
+        <v>605</v>
       </c>
       <c r="AM97" t="s" s="2">
         <v>21</v>
@@ -14051,10 +14054,10 @@
     </row>
     <row r="98" hidden="true">
       <c r="A98" t="s" s="2">
-        <v>605</v>
+        <v>606</v>
       </c>
       <c r="B98" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C98" s="2"/>
       <c r="D98" t="s" s="2">
@@ -14143,7 +14146,7 @@
         <v>88</v>
       </c>
       <c r="AI98" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AJ98" t="s" s="2">
         <v>21</v>
@@ -14166,10 +14169,10 @@
     </row>
     <row r="99" hidden="true">
       <c r="A99" t="s" s="2">
-        <v>607</v>
+        <v>608</v>
       </c>
       <c r="B99" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C99" s="2"/>
       <c r="D99" t="s" s="2">
@@ -14195,10 +14198,10 @@
         <v>109</v>
       </c>
       <c r="L99" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M99" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N99" s="2"/>
       <c r="O99" s="2"/>
@@ -14281,10 +14284,10 @@
     </row>
     <row r="100" hidden="true">
       <c r="A100" t="s" s="2">
-        <v>609</v>
+        <v>610</v>
       </c>
       <c r="B100" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C100" s="2"/>
       <c r="D100" t="s" s="2">
@@ -14310,13 +14313,13 @@
         <v>135</v>
       </c>
       <c r="L100" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M100" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N100" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O100" s="2"/>
       <c r="P100" t="s" s="2">
@@ -14324,7 +14327,7 @@
       </c>
       <c r="Q100" s="2"/>
       <c r="R100" t="s" s="2">
-        <v>611</v>
+        <v>612</v>
       </c>
       <c r="S100" t="s" s="2">
         <v>21</v>
@@ -14366,7 +14369,7 @@
         <v>21</v>
       </c>
       <c r="AF100" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG100" t="s" s="2">
         <v>88</v>
@@ -14398,10 +14401,10 @@
     </row>
     <row r="101" hidden="true">
       <c r="A101" t="s" s="2">
-        <v>612</v>
+        <v>613</v>
       </c>
       <c r="B101" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C101" s="2"/>
       <c r="D101" t="s" s="2">
@@ -14427,10 +14430,10 @@
         <v>347</v>
       </c>
       <c r="L101" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M101" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N101" s="2"/>
       <c r="O101" s="2"/>
@@ -14469,7 +14472,7 @@
         <v>21</v>
       </c>
       <c r="AB101" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AC101" s="2"/>
       <c r="AD101" t="s" s="2">
@@ -14479,7 +14482,7 @@
         <v>115</v>
       </c>
       <c r="AF101" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG101" t="s" s="2">
         <v>80</v>
@@ -14488,7 +14491,7 @@
         <v>88</v>
       </c>
       <c r="AI101" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AJ101" t="s" s="2">
         <v>100</v>
@@ -14511,13 +14514,13 @@
     </row>
     <row r="102" hidden="true">
       <c r="A102" t="s" s="2">
-        <v>617</v>
+        <v>618</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>598</v>
+        <v>599</v>
       </c>
       <c r="C102" t="s" s="2">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="D102" t="s" s="2">
         <v>21</v>
@@ -14527,7 +14530,7 @@
         <v>80</v>
       </c>
       <c r="G102" t="s" s="2">
-        <v>88</v>
+        <v>81</v>
       </c>
       <c r="H102" t="s" s="2">
         <v>21</v>
@@ -14539,13 +14542,13 @@
         <v>21</v>
       </c>
       <c r="K102" t="s" s="2">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L102" t="s" s="2">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M102" t="s" s="2">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N102" s="2"/>
       <c r="O102" s="2"/>
@@ -14605,16 +14608,16 @@
         <v>81</v>
       </c>
       <c r="AI102" t="s" s="2">
-        <v>21</v>
+        <v>500</v>
       </c>
       <c r="AJ102" t="s" s="2">
-        <v>117</v>
+        <v>501</v>
       </c>
       <c r="AK102" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL102" t="s" s="2">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="AM102" t="s" s="2">
         <v>21</v>
@@ -14628,10 +14631,10 @@
     </row>
     <row r="103" hidden="true">
       <c r="A103" t="s" s="2">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="B103" t="s" s="2">
-        <v>606</v>
+        <v>607</v>
       </c>
       <c r="C103" s="2"/>
       <c r="D103" t="s" s="2">
@@ -14720,7 +14723,7 @@
         <v>88</v>
       </c>
       <c r="AI103" t="s" s="2">
-        <v>499</v>
+        <v>500</v>
       </c>
       <c r="AJ103" t="s" s="2">
         <v>21</v>
@@ -14743,10 +14746,10 @@
     </row>
     <row r="104" hidden="true">
       <c r="A104" t="s" s="2">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="B104" t="s" s="2">
-        <v>608</v>
+        <v>609</v>
       </c>
       <c r="C104" s="2"/>
       <c r="D104" t="s" s="2">
@@ -14772,10 +14775,10 @@
         <v>109</v>
       </c>
       <c r="L104" t="s" s="2">
-        <v>492</v>
+        <v>493</v>
       </c>
       <c r="M104" t="s" s="2">
-        <v>493</v>
+        <v>494</v>
       </c>
       <c r="N104" s="2"/>
       <c r="O104" s="2"/>
@@ -14858,10 +14861,10 @@
     </row>
     <row r="105" hidden="true">
       <c r="A105" t="s" s="2">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="B105" t="s" s="2">
-        <v>610</v>
+        <v>611</v>
       </c>
       <c r="C105" s="2"/>
       <c r="D105" t="s" s="2">
@@ -14887,13 +14890,13 @@
         <v>135</v>
       </c>
       <c r="L105" t="s" s="2">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="M105" t="s" s="2">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="N105" t="s" s="2">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="O105" s="2"/>
       <c r="P105" t="s" s="2">
@@ -14901,7 +14904,7 @@
       </c>
       <c r="Q105" s="2"/>
       <c r="R105" t="s" s="2">
-        <v>626</v>
+        <v>627</v>
       </c>
       <c r="S105" t="s" s="2">
         <v>21</v>
@@ -14943,7 +14946,7 @@
         <v>21</v>
       </c>
       <c r="AF105" t="s" s="2">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="AG105" t="s" s="2">
         <v>88</v>
@@ -14975,10 +14978,10 @@
     </row>
     <row r="106" hidden="true">
       <c r="A106" t="s" s="2">
-        <v>627</v>
+        <v>628</v>
       </c>
       <c r="B106" t="s" s="2">
-        <v>613</v>
+        <v>614</v>
       </c>
       <c r="C106" s="2"/>
       <c r="D106" t="s" s="2">
@@ -15004,10 +15007,10 @@
         <v>102</v>
       </c>
       <c r="L106" t="s" s="2">
-        <v>520</v>
+        <v>522</v>
       </c>
       <c r="M106" t="s" s="2">
-        <v>614</v>
+        <v>615</v>
       </c>
       <c r="N106" s="2"/>
       <c r="O106" s="2"/>
@@ -15046,7 +15049,7 @@
         <v>21</v>
       </c>
       <c r="AB106" t="s" s="2">
-        <v>615</v>
+        <v>616</v>
       </c>
       <c r="AC106" s="2"/>
       <c r="AD106" t="s" s="2">
@@ -15056,7 +15059,7 @@
         <v>115</v>
       </c>
       <c r="AF106" t="s" s="2">
-        <v>522</v>
+        <v>524</v>
       </c>
       <c r="AG106" t="s" s="2">
         <v>80</v>
@@ -15065,7 +15068,7 @@
         <v>88</v>
       </c>
       <c r="AI106" t="s" s="2">
-        <v>616</v>
+        <v>617</v>
       </c>
       <c r="AJ106" t="s" s="2">
         <v>100</v>
@@ -15088,10 +15091,10 @@
     </row>
     <row r="107" hidden="true">
       <c r="A107" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>628</v>
+        <v>629</v>
       </c>
       <c r="C107" s="2"/>
       <c r="D107" t="s" s="2">
@@ -15117,10 +15120,10 @@
         <v>102</v>
       </c>
       <c r="L107" t="s" s="2">
-        <v>629</v>
+        <v>630</v>
       </c>
       <c r="M107" t="s" s="2">
-        <v>630</v>
+        <v>631</v>
       </c>
       <c r="N107" s="2"/>
       <c r="O107" s="2"/>
@@ -15144,7 +15147,7 @@
         <v>21</v>
       </c>
       <c r="W107" t="s" s="2">
-        <v>631</v>
+        <v>632</v>
       </c>
       <c r="X107" t="s" s="2">
         <v>21</v>
@@ -15171,7 +15174,7 @@
         <v>21</v>
       </c>
       <c r="AF107" t="s" s="2">
-        <v>632</v>
+        <v>633</v>
       </c>
       <c r="AG107" t="s" s="2">
         <v>80</v>
@@ -15203,10 +15206,10 @@
     </row>
     <row r="108">
       <c r="A108" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="C108" s="2"/>
       <c r="D108" t="s" s="2">
@@ -15232,16 +15235,16 @@
         <v>169</v>
       </c>
       <c r="L108" t="s" s="2">
-        <v>634</v>
+        <v>635</v>
       </c>
       <c r="M108" t="s" s="2">
-        <v>635</v>
+        <v>636</v>
       </c>
       <c r="N108" t="s" s="2">
-        <v>636</v>
+        <v>637</v>
       </c>
       <c r="O108" t="s" s="2">
-        <v>637</v>
+        <v>638</v>
       </c>
       <c r="P108" t="s" s="2">
         <v>21</v>
@@ -15269,10 +15272,10 @@
         <v>225</v>
       </c>
       <c r="Y108" t="s" s="2">
-        <v>638</v>
+        <v>639</v>
       </c>
       <c r="Z108" t="s" s="2">
-        <v>639</v>
+        <v>640</v>
       </c>
       <c r="AA108" t="s" s="2">
         <v>21</v>
@@ -15290,7 +15293,7 @@
         <v>21</v>
       </c>
       <c r="AF108" t="s" s="2">
-        <v>633</v>
+        <v>634</v>
       </c>
       <c r="AG108" t="s" s="2">
         <v>88</v>
@@ -15308,7 +15311,7 @@
         <v>21</v>
       </c>
       <c r="AL108" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM108" t="s" s="2">
         <v>21</v>
@@ -15322,10 +15325,10 @@
     </row>
     <row r="109" hidden="true">
       <c r="A109" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="B109" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="C109" s="2"/>
       <c r="D109" t="s" s="2">
@@ -15348,19 +15351,19 @@
         <v>21</v>
       </c>
       <c r="K109" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L109" t="s" s="2">
-        <v>642</v>
+        <v>643</v>
       </c>
       <c r="M109" t="s" s="2">
-        <v>643</v>
+        <v>644</v>
       </c>
       <c r="N109" t="s" s="2">
-        <v>644</v>
+        <v>645</v>
       </c>
       <c r="O109" t="s" s="2">
-        <v>645</v>
+        <v>646</v>
       </c>
       <c r="P109" t="s" s="2">
         <v>21</v>
@@ -15409,7 +15412,7 @@
         <v>21</v>
       </c>
       <c r="AF109" t="s" s="2">
-        <v>641</v>
+        <v>642</v>
       </c>
       <c r="AG109" t="s" s="2">
         <v>80</v>
@@ -15421,13 +15424,13 @@
         <v>21</v>
       </c>
       <c r="AJ109" t="s" s="2">
-        <v>646</v>
+        <v>647</v>
       </c>
       <c r="AK109" t="s" s="2">
         <v>21</v>
       </c>
       <c r="AL109" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM109" t="s" s="2">
         <v>21</v>
@@ -15441,10 +15444,10 @@
     </row>
     <row r="110" hidden="true">
       <c r="A110" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="B110" t="s" s="2">
-        <v>647</v>
+        <v>648</v>
       </c>
       <c r="C110" s="2"/>
       <c r="D110" t="s" s="2">
@@ -15556,10 +15559,10 @@
     </row>
     <row r="111" hidden="true">
       <c r="A111" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="B111" t="s" s="2">
-        <v>648</v>
+        <v>649</v>
       </c>
       <c r="C111" s="2"/>
       <c r="D111" t="s" s="2">
@@ -15673,14 +15676,14 @@
     </row>
     <row r="112" hidden="true">
       <c r="A112" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>649</v>
+        <v>650</v>
       </c>
       <c r="C112" s="2"/>
       <c r="D112" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E112" s="2"/>
       <c r="F112" t="s" s="2">
@@ -15702,10 +15705,10 @@
         <v>109</v>
       </c>
       <c r="L112" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M112" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N112" t="s" s="2">
         <v>112</v>
@@ -15760,7 +15763,7 @@
         <v>21</v>
       </c>
       <c r="AF112" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG112" t="s" s="2">
         <v>80</v>
@@ -15792,10 +15795,10 @@
     </row>
     <row r="113" hidden="true">
       <c r="A113" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="C113" s="2"/>
       <c r="D113" t="s" s="2">
@@ -15821,13 +15824,13 @@
         <v>102</v>
       </c>
       <c r="L113" t="s" s="2">
-        <v>651</v>
+        <v>652</v>
       </c>
       <c r="M113" t="s" s="2">
-        <v>652</v>
+        <v>653</v>
       </c>
       <c r="N113" t="s" s="2">
-        <v>653</v>
+        <v>654</v>
       </c>
       <c r="O113" s="2"/>
       <c r="P113" t="s" s="2">
@@ -15877,7 +15880,7 @@
         <v>21</v>
       </c>
       <c r="AF113" t="s" s="2">
-        <v>650</v>
+        <v>651</v>
       </c>
       <c r="AG113" t="s" s="2">
         <v>88</v>
@@ -15895,7 +15898,7 @@
         <v>21</v>
       </c>
       <c r="AL113" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM113" t="s" s="2">
         <v>21</v>
@@ -15909,10 +15912,10 @@
     </row>
     <row r="114" hidden="true">
       <c r="A114" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="B114" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="C114" s="2"/>
       <c r="D114" t="s" s="2">
@@ -15938,10 +15941,10 @@
         <v>169</v>
       </c>
       <c r="L114" t="s" s="2">
-        <v>655</v>
+        <v>656</v>
       </c>
       <c r="M114" t="s" s="2">
-        <v>656</v>
+        <v>657</v>
       </c>
       <c r="N114" s="2"/>
       <c r="O114" s="2"/>
@@ -15971,10 +15974,10 @@
         <v>225</v>
       </c>
       <c r="Y114" t="s" s="2">
-        <v>657</v>
+        <v>658</v>
       </c>
       <c r="Z114" t="s" s="2">
-        <v>658</v>
+        <v>659</v>
       </c>
       <c r="AA114" t="s" s="2">
         <v>21</v>
@@ -15992,7 +15995,7 @@
         <v>21</v>
       </c>
       <c r="AF114" t="s" s="2">
-        <v>654</v>
+        <v>655</v>
       </c>
       <c r="AG114" t="s" s="2">
         <v>88</v>
@@ -16010,7 +16013,7 @@
         <v>21</v>
       </c>
       <c r="AL114" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM114" t="s" s="2">
         <v>21</v>
@@ -16024,10 +16027,10 @@
     </row>
     <row r="115" hidden="true">
       <c r="A115" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="C115" s="2"/>
       <c r="D115" t="s" s="2">
@@ -16050,13 +16053,13 @@
         <v>21</v>
       </c>
       <c r="K115" t="s" s="2">
-        <v>660</v>
+        <v>661</v>
       </c>
       <c r="L115" t="s" s="2">
-        <v>661</v>
+        <v>662</v>
       </c>
       <c r="M115" t="s" s="2">
-        <v>662</v>
+        <v>663</v>
       </c>
       <c r="N115" s="2"/>
       <c r="O115" s="2"/>
@@ -16086,10 +16089,10 @@
         <v>159</v>
       </c>
       <c r="Y115" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="Z115" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AA115" t="s" s="2">
         <v>21</v>
@@ -16107,7 +16110,7 @@
         <v>21</v>
       </c>
       <c r="AF115" t="s" s="2">
-        <v>659</v>
+        <v>660</v>
       </c>
       <c r="AG115" t="s" s="2">
         <v>88</v>
@@ -16116,7 +16119,7 @@
         <v>88</v>
       </c>
       <c r="AI115" t="s" s="2">
-        <v>665</v>
+        <v>666</v>
       </c>
       <c r="AJ115" t="s" s="2">
         <v>100</v>
@@ -16125,7 +16128,7 @@
         <v>21</v>
       </c>
       <c r="AL115" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM115" t="s" s="2">
         <v>21</v>
@@ -16139,10 +16142,10 @@
     </row>
     <row r="116" hidden="true">
       <c r="A116" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="C116" s="2"/>
       <c r="D116" t="s" s="2">
@@ -16168,13 +16171,13 @@
         <v>169</v>
       </c>
       <c r="L116" t="s" s="2">
-        <v>667</v>
+        <v>668</v>
       </c>
       <c r="M116" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="N116" t="s" s="2">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="O116" s="2"/>
       <c r="P116" t="s" s="2">
@@ -16203,10 +16206,10 @@
         <v>225</v>
       </c>
       <c r="Y116" t="s" s="2">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="Z116" t="s" s="2">
-        <v>670</v>
+        <v>671</v>
       </c>
       <c r="AA116" t="s" s="2">
         <v>21</v>
@@ -16224,7 +16227,7 @@
         <v>21</v>
       </c>
       <c r="AF116" t="s" s="2">
-        <v>666</v>
+        <v>667</v>
       </c>
       <c r="AG116" t="s" s="2">
         <v>80</v>
@@ -16233,7 +16236,7 @@
         <v>88</v>
       </c>
       <c r="AI116" t="s" s="2">
-        <v>671</v>
+        <v>672</v>
       </c>
       <c r="AJ116" t="s" s="2">
         <v>100</v>
@@ -16242,7 +16245,7 @@
         <v>21</v>
       </c>
       <c r="AL116" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM116" t="s" s="2">
         <v>21</v>
@@ -16256,10 +16259,10 @@
     </row>
     <row r="117" hidden="true">
       <c r="A117" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="B117" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="C117" s="2"/>
       <c r="D117" t="s" s="2">
@@ -16285,20 +16288,20 @@
         <v>308</v>
       </c>
       <c r="L117" t="s" s="2">
-        <v>673</v>
+        <v>674</v>
       </c>
       <c r="M117" t="s" s="2">
-        <v>674</v>
+        <v>675</v>
       </c>
       <c r="N117" t="s" s="2">
-        <v>675</v>
+        <v>676</v>
       </c>
       <c r="O117" s="2"/>
       <c r="P117" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q117" t="s" s="2">
-        <v>676</v>
+        <v>677</v>
       </c>
       <c r="R117" t="s" s="2">
         <v>21</v>
@@ -16343,7 +16346,7 @@
         <v>21</v>
       </c>
       <c r="AF117" t="s" s="2">
-        <v>672</v>
+        <v>673</v>
       </c>
       <c r="AG117" t="s" s="2">
         <v>80</v>
@@ -16352,7 +16355,7 @@
         <v>88</v>
       </c>
       <c r="AI117" t="s" s="2">
-        <v>677</v>
+        <v>678</v>
       </c>
       <c r="AJ117" t="s" s="2">
         <v>100</v>
@@ -16361,7 +16364,7 @@
         <v>21</v>
       </c>
       <c r="AL117" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM117" t="s" s="2">
         <v>21</v>
@@ -16375,10 +16378,10 @@
     </row>
     <row r="118" hidden="true">
       <c r="A118" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="B118" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C118" s="2"/>
       <c r="D118" t="s" s="2">
@@ -16404,76 +16407,76 @@
         <v>308</v>
       </c>
       <c r="L118" t="s" s="2">
+        <v>680</v>
+      </c>
+      <c r="M118" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="N118" t="s" s="2">
+        <v>682</v>
+      </c>
+      <c r="O118" t="s" s="2">
+        <v>683</v>
+      </c>
+      <c r="P118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Q118" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="R118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="S118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="T118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="U118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="V118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="W118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="X118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Y118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="Z118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AA118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AB118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AC118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AD118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AE118" t="s" s="2">
+        <v>21</v>
+      </c>
+      <c r="AF118" t="s" s="2">
         <v>679</v>
       </c>
-      <c r="M118" t="s" s="2">
-        <v>680</v>
-      </c>
-      <c r="N118" t="s" s="2">
-        <v>681</v>
-      </c>
-      <c r="O118" t="s" s="2">
-        <v>682</v>
-      </c>
-      <c r="P118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Q118" t="s" s="2">
-        <v>683</v>
-      </c>
-      <c r="R118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="S118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="T118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="U118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="V118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="W118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="X118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Y118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="Z118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AA118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AB118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AC118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AD118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AE118" t="s" s="2">
-        <v>21</v>
-      </c>
-      <c r="AF118" t="s" s="2">
+      <c r="AG118" t="s" s="2">
+        <v>80</v>
+      </c>
+      <c r="AH118" t="s" s="2">
+        <v>88</v>
+      </c>
+      <c r="AI118" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="AG118" t="s" s="2">
-        <v>80</v>
-      </c>
-      <c r="AH118" t="s" s="2">
-        <v>88</v>
-      </c>
-      <c r="AI118" t="s" s="2">
-        <v>677</v>
       </c>
       <c r="AJ118" t="s" s="2">
         <v>100</v>
@@ -16482,7 +16485,7 @@
         <v>21</v>
       </c>
       <c r="AL118" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM118" t="s" s="2">
         <v>21</v>
@@ -16496,10 +16499,10 @@
     </row>
     <row r="119" hidden="true">
       <c r="A119" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="B119" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="C119" s="2"/>
       <c r="D119" t="s" s="2">
@@ -16525,16 +16528,16 @@
         <v>308</v>
       </c>
       <c r="L119" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="M119" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N119" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="O119" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="P119" t="s" s="2">
         <v>21</v>
@@ -16583,7 +16586,7 @@
         <v>21</v>
       </c>
       <c r="AF119" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="AG119" t="s" s="2">
         <v>80</v>
@@ -16592,7 +16595,7 @@
         <v>88</v>
       </c>
       <c r="AI119" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="AJ119" t="s" s="2">
         <v>100</v>
@@ -16601,7 +16604,7 @@
         <v>21</v>
       </c>
       <c r="AL119" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM119" t="s" s="2">
         <v>21</v>
@@ -16615,10 +16618,10 @@
     </row>
     <row r="120" hidden="true">
       <c r="A120" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="B120" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C120" s="2"/>
       <c r="D120" t="s" s="2">
@@ -16641,16 +16644,16 @@
         <v>21</v>
       </c>
       <c r="K120" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="L120" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="M120" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="N120" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="O120" s="2"/>
       <c r="P120" t="s" s="2">
@@ -16700,7 +16703,7 @@
         <v>21</v>
       </c>
       <c r="AF120" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="AG120" t="s" s="2">
         <v>80</v>
@@ -16709,7 +16712,7 @@
         <v>88</v>
       </c>
       <c r="AI120" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="AJ120" t="s" s="2">
         <v>100</v>
@@ -16718,7 +16721,7 @@
         <v>21</v>
       </c>
       <c r="AL120" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM120" t="s" s="2">
         <v>21</v>
@@ -16732,10 +16735,10 @@
     </row>
     <row r="121" hidden="true">
       <c r="A121" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="B121" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="C121" s="2"/>
       <c r="D121" t="s" s="2">
@@ -16758,16 +16761,16 @@
         <v>21</v>
       </c>
       <c r="K121" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="L121" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="M121" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="N121" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="O121" s="2"/>
       <c r="P121" t="s" s="2">
@@ -16817,7 +16820,7 @@
         <v>21</v>
       </c>
       <c r="AF121" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="AG121" t="s" s="2">
         <v>80</v>
@@ -16826,7 +16829,7 @@
         <v>88</v>
       </c>
       <c r="AI121" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AJ121" t="s" s="2">
         <v>100</v>
@@ -16835,7 +16838,7 @@
         <v>21</v>
       </c>
       <c r="AL121" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM121" t="s" s="2">
         <v>21</v>
@@ -16849,10 +16852,10 @@
     </row>
     <row r="122" hidden="true">
       <c r="A122" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="B122" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="C122" s="2"/>
       <c r="D122" t="s" s="2">
@@ -16875,16 +16878,16 @@
         <v>21</v>
       </c>
       <c r="K122" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L122" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="M122" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="N122" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="O122" s="2"/>
       <c r="P122" t="s" s="2">
@@ -16934,7 +16937,7 @@
         <v>21</v>
       </c>
       <c r="AF122" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="AG122" t="s" s="2">
         <v>80</v>
@@ -16943,7 +16946,7 @@
         <v>81</v>
       </c>
       <c r="AI122" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="AJ122" t="s" s="2">
         <v>100</v>
@@ -16952,7 +16955,7 @@
         <v>21</v>
       </c>
       <c r="AL122" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM122" t="s" s="2">
         <v>21</v>
@@ -16966,10 +16969,10 @@
     </row>
     <row r="123" hidden="true">
       <c r="A123" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="B123" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="C123" s="2"/>
       <c r="D123" t="s" s="2">
@@ -17081,10 +17084,10 @@
     </row>
     <row r="124" hidden="true">
       <c r="A124" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="C124" s="2"/>
       <c r="D124" t="s" s="2">
@@ -17198,14 +17201,14 @@
     </row>
     <row r="125" hidden="true">
       <c r="A125" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="B125" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="C125" s="2"/>
       <c r="D125" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E125" s="2"/>
       <c r="F125" t="s" s="2">
@@ -17227,10 +17230,10 @@
         <v>109</v>
       </c>
       <c r="L125" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M125" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N125" t="s" s="2">
         <v>112</v>
@@ -17285,7 +17288,7 @@
         <v>21</v>
       </c>
       <c r="AF125" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG125" t="s" s="2">
         <v>80</v>
@@ -17317,10 +17320,10 @@
     </row>
     <row r="126" hidden="true">
       <c r="A126" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="B126" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="C126" s="2"/>
       <c r="D126" t="s" s="2">
@@ -17343,16 +17346,16 @@
         <v>21</v>
       </c>
       <c r="K126" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="L126" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="M126" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="N126" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="O126" s="2"/>
       <c r="P126" t="s" s="2">
@@ -17381,10 +17384,10 @@
         <v>159</v>
       </c>
       <c r="Y126" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="Z126" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AA126" t="s" s="2">
         <v>21</v>
@@ -17402,7 +17405,7 @@
         <v>21</v>
       </c>
       <c r="AF126" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AG126" t="s" s="2">
         <v>88</v>
@@ -17420,7 +17423,7 @@
         <v>21</v>
       </c>
       <c r="AL126" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM126" t="s" s="2">
         <v>21</v>
@@ -17434,10 +17437,10 @@
     </row>
     <row r="127" hidden="true">
       <c r="A127" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="B127" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="C127" s="2"/>
       <c r="D127" t="s" s="2">
@@ -17463,20 +17466,20 @@
         <v>308</v>
       </c>
       <c r="L127" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="M127" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N127" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O127" s="2"/>
       <c r="P127" t="s" s="2">
         <v>21</v>
       </c>
       <c r="Q127" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="R127" t="s" s="2">
         <v>21</v>
@@ -17521,7 +17524,7 @@
         <v>21</v>
       </c>
       <c r="AF127" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AG127" t="s" s="2">
         <v>80</v>
@@ -17539,7 +17542,7 @@
         <v>21</v>
       </c>
       <c r="AL127" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM127" t="s" s="2">
         <v>21</v>
@@ -17553,10 +17556,10 @@
     </row>
     <row r="128" hidden="true">
       <c r="A128" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="B128" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="C128" s="2"/>
       <c r="D128" t="s" s="2">
@@ -17579,19 +17582,19 @@
         <v>21</v>
       </c>
       <c r="K128" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="L128" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="M128" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="N128" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="O128" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="P128" t="s" s="2">
         <v>21</v>
@@ -17640,7 +17643,7 @@
         <v>21</v>
       </c>
       <c r="AF128" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="AG128" t="s" s="2">
         <v>80</v>
@@ -17649,7 +17652,7 @@
         <v>81</v>
       </c>
       <c r="AI128" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="AJ128" t="s" s="2">
         <v>100</v>
@@ -17658,7 +17661,7 @@
         <v>21</v>
       </c>
       <c r="AL128" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM128" t="s" s="2">
         <v>21</v>
@@ -17672,10 +17675,10 @@
     </row>
     <row r="129" hidden="true">
       <c r="A129" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="C129" s="2"/>
       <c r="D129" t="s" s="2">
@@ -17787,10 +17790,10 @@
     </row>
     <row r="130" hidden="true">
       <c r="A130" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="C130" s="2"/>
       <c r="D130" t="s" s="2">
@@ -17904,14 +17907,14 @@
     </row>
     <row r="131" hidden="true">
       <c r="A131" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="B131" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="C131" s="2"/>
       <c r="D131" t="s" s="2">
-        <v>561</v>
+        <v>563</v>
       </c>
       <c r="E131" s="2"/>
       <c r="F131" t="s" s="2">
@@ -17933,10 +17936,10 @@
         <v>109</v>
       </c>
       <c r="L131" t="s" s="2">
-        <v>562</v>
+        <v>564</v>
       </c>
       <c r="M131" t="s" s="2">
-        <v>563</v>
+        <v>565</v>
       </c>
       <c r="N131" t="s" s="2">
         <v>112</v>
@@ -17991,7 +17994,7 @@
         <v>21</v>
       </c>
       <c r="AF131" t="s" s="2">
-        <v>564</v>
+        <v>566</v>
       </c>
       <c r="AG131" t="s" s="2">
         <v>80</v>
@@ -18023,10 +18026,10 @@
     </row>
     <row r="132" hidden="true">
       <c r="A132" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="B132" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C132" s="2"/>
       <c r="D132" t="s" s="2">
@@ -18049,16 +18052,16 @@
         <v>21</v>
       </c>
       <c r="K132" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="L132" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="M132" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="N132" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="O132" s="2"/>
       <c r="P132" t="s" s="2">
@@ -18087,10 +18090,10 @@
         <v>159</v>
       </c>
       <c r="Y132" t="s" s="2">
-        <v>663</v>
+        <v>664</v>
       </c>
       <c r="Z132" t="s" s="2">
-        <v>664</v>
+        <v>665</v>
       </c>
       <c r="AA132" t="s" s="2">
         <v>21</v>
@@ -18108,7 +18111,7 @@
         <v>21</v>
       </c>
       <c r="AF132" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AG132" t="s" s="2">
         <v>88</v>
@@ -18126,7 +18129,7 @@
         <v>21</v>
       </c>
       <c r="AL132" t="s" s="2">
-        <v>640</v>
+        <v>641</v>
       </c>
       <c r="AM132" t="s" s="2">
         <v>21</v>
@@ -18140,10 +18143,10 @@
     </row>
     <row r="133" hidden="true">
       <c r="A133" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="B133" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="C133" s="2"/>
       <c r="D133" t="s" s="2">
@@ -18169,16 +18172,16 @@
         <v>21</v>
       </c>
       <c r="L133" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="M133" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="N133" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="O133" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="P133" t="s" s="2">
         <v>21</v>
@@ -18227,7 +18230,7 @@
         <v>21</v>
       </c>
       <c r="AF133" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="AG133" t="s" s="2">
         <v>80</v>
@@ -18236,7 +18239,7 @@
         <v>81</v>
       </c>
       <c r="AI133" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="AJ133" t="s" s="2">
         <v>100</v>
@@ -18245,7 +18248,7 @@
         <v>21</v>
       </c>
       <c r="AL133" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="AM133" t="s" s="2">
         <v>21</v>
